--- a/mappingCorps/ig/FRServiceRequestLMCDAFHIR.xlsx
+++ b/mappingCorps/ig/FRServiceRequestLMCDAFHIR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T08:18:14+00:00</t>
+    <t>2026-08-05T09:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mapping des éléments du modèle métier FRLMDemandeExamenOuSuivi vers le profil CDA FRCDADemandeDExamenOuDeSuivi, puis vers le profil FHIR FRServiceRequestDocument.</t>
+    <t>Mapping des éléments du modèle métier FRLMServiceRequest vers le profil CDA FRCDADemandeDExamenOuDeSuivi, puis vers le profil FHIR FRServiceRequestDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -100,7 +100,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-demande-examen-ou-suivi</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-service-request</t>
   </si>
   <si>
     <t/>
@@ -109,7 +109,7 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-demande-d-examen-ou-de-suivi</t>
   </si>
   <si>
-    <t>FRLMDemandeExamenOuSuivi</t>
+    <t>FRLMServiceRequest</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -118,106 +118,109 @@
     <t>FRCDADemandeDExamenOuDeSuivi</t>
   </si>
   <si>
-    <t>FRLMDemandeExamenOuSuivi.identifiant</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.id</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.typeDemande</t>
+    <t>FRLMServiceRequest.header.status</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.statusCode</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.code</t>
   </si>
   <si>
     <t>FRCDADemandeDExamenOuDeSuivi.code</t>
   </si>
   <si>
-    <t>FRLMDemandeExamenOuSuivi.description</t>
+    <t>FRLMServiceRequest.bodySite</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.targetSiteCode</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.reason[x]</t>
+  </si>
+  <si>
+    <t>related-to</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.reasonCode</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.priority</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.priorityCode</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.supportingInformation[x]</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.observation</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.specimen</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.specimen</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.encounter</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.entryRelationship.encounter</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.occurrence[x]</t>
+  </si>
+  <si>
+    <t>FRCDADemandeDExamenOuDeSuivi.effectiveTime</t>
+  </si>
+  <si>
+    <t>FRLMServiceRequest.patientInstructions</t>
   </si>
   <si>
     <t>FRCDADemandeDExamenOuDeSuivi.text</t>
   </si>
   <si>
-    <t>FRLMDemandeExamenOuSuivi.statutDemande</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.statusCode</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.date</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.effectiveTime</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.resultat</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.value</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.interpretation</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.interpretationCode</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.methode</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.methodCode</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.cible</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.targetSiteCode</t>
-  </si>
-  <si>
-    <t>FRLMDemandeExamenOuSuivi.auteur</t>
-  </si>
-  <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.author</t>
-  </si>
-  <si>
     <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-service-request-document</t>
   </si>
   <si>
     <t>FRServiceRequestDocument</t>
   </si>
   <si>
-    <t>FRCDADemandeDExamenOuDeSuivi.moodCode</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.intent</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.identifier</t>
+    <t>FRServiceRequestDocument.status</t>
   </si>
   <si>
     <t>FRServiceRequestDocument.code</t>
   </si>
   <si>
+    <t>FRLMServiceRequest.quantity</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.quantity</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.bodySite</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.reasonCode</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.priority</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.supportingInfo</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.specimen</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.encounter</t>
+  </si>
+  <si>
+    <t>FRServiceRequestDocument.occurrence[x]</t>
+  </si>
+  <si>
     <t>FRServiceRequestDocument.note</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.status</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.occurrence[x]</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.orderDetail.coding</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.extension:interpretation</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.extension:method</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.bodySite</t>
-  </si>
-  <si>
-    <t>FRServiceRequestDocument.requester.extension:author</t>
   </si>
 </sst>
 </file>
@@ -564,88 +567,88 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -678,7 +681,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>29</v>
@@ -687,7 +690,7 @@
         <v>29</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>29</v>
@@ -695,20 +698,20 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
@@ -721,7 +724,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
@@ -734,40 +737,40 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>32</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -780,7 +783,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -793,7 +796,7 @@
         <v>32</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -806,7 +809,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2"/>
     </row>
@@ -819,7 +822,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2"/>
     </row>
@@ -832,7 +835,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -845,7 +848,7 @@
         <v>32</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2"/>
     </row>
